--- a/problems/marketing/1.youth_policy/데이터/2_추천리스트_제출용.xlsx
+++ b/problems/marketing/1.youth_policy/데이터/2_추천리스트_제출용.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="타게팅" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타게팅" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>회원 만 나이가 정책 연령(연령_min~연령_max, 양끝 포함) 안. 만 나이 = 기준일(2026-06-28) 기준이며, 생일이 아직 안 지났으면 한 살 뺀다(연도만 빼면 틀림)</t>
+          <t>회원 만 나이가 정책 연령(연령_최소~연령_최대, 양끝 포함) 안. 만 나이 = 기준일(2026-06-28) 기준이며, 생일이 아직 안 지났으면 한 살 뺀다(연도만 빼면 틀림)</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>소득상한_월_원이 있으면 회원 월소득_원이 그 이하(같으면 통과) / 빈칸=모두</t>
+          <t>월소득상한(원)이 있으면 회원 월소득(원)이 그 이하(같으면 통과) / 빈칸=모두</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>연소득상한_원이 있으면 회원 연소득_원이 그 이하(같으면 통과). 월소득과 별개 / 빈칸=모두</t>
+          <t>연소득상한(원)이 있으면 회원 연소득(원)이 그 이하(같으면 통과). 월소득과 별개 / 빈칸=모두</t>
         </is>
       </c>
     </row>

--- a/problems/marketing/1.youth_policy/데이터/2_추천리스트_제출용.xlsx
+++ b/problems/marketing/1.youth_policy/데이터/2_추천리스트_제출용.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타게팅" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="타게팅" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="소득기준표" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -579,7 +580,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>월소득</t>
+          <t>월소득(본인상한)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -591,82 +592,106 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>연소득</t>
+          <t>월소득(중위소득%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>연소득상한(원)이 있으면 회원 연소득(원)이 그 이하(같으면 통과). 월소득과 별개 / 빈칸=모두</t>
+          <t>정책에 '월소득_중위소득기준(%)'가 있으면, 회원 '가구원수'에 해당하는 상한 금액 이하라야 통과(같으면 통과). 상한 = 이 파일 '소득기준표' 시트에서 그 가구원수·그 % 칸의 금액. 가구원수가 크면 상한도 커진다 / 빈칸=모두</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>무주택</t>
+          <t>연소득</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>무주택요건이 '필요'면 회원 주택소유여부가 '아니오' / 빈칸=모두</t>
+          <t>연소득상한(원)이 있으면 회원 연소득(원)이 그 이하(같으면 통과). 월소득과 별개 / 빈칸=모두</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>학력</t>
+          <t>★소득기준표</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>학력요건 '재학'=회원 재학상태가 재학 또는 휴학 / '졸업'=졸업 / 빈칸=모두</t>
+          <t>이 파일의 '소득기준표' 시트에 가구원수별 기준 중위소득(월)과 비율별(예 150%) 상한 금액이 계산돼 있다. 중위소득 % 정책은 회원 가구원수로 이 표를 찾아 상한을 정한다(직접 계산: 기준중위소득×%÷100, 원단위 반올림)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>혼인</t>
+          <t>무주택</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>혼인요건 '신혼부부'=회원 혼인여부 기혼 / '미혼'=미혼 / 빈칸=모두</t>
+          <t>무주택요건이 '필요'면 회원 주택소유여부가 '아니오' / 빈칸=모두</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>★확인 불가 정책</t>
+          <t>학력</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>회원 명단(2_회원명단.xlsx의 컬럼)만으로는 자격을 끝까지 확인할 수 없는 정책이 섞여 있을 수 있다. 그런 정책은 아무에게도 추천하지 않는다 — 확실할 때만 추천하고, 무리하면 오발송(FP)이다</t>
+          <t>학력요건 '재학'=회원 재학상태가 재학 또는 휴학 / '졸업'=졸업 / 빈칸=모두</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>행 순서</t>
+          <t>혼인</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>채점에 영향 없음. 중복 행은 1개로 간주</t>
+          <t>혼인요건 '신혼부부'=회원 혼인여부 기혼 / '미혼'=미혼 / 빈칸=모두</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>★확인 불가 정책</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>회원 명단(2_회원명단.xlsx의 컬럼)만으로는 자격을 끝까지 확인할 수 없는 정책이 섞여 있을 수 있다. 그런 정책은 아무에게도 추천하지 않는다 — 확실할 때만 추천하고, 무리하면 오발송(FP)이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>행 순서</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>채점에 영향 없음. 중복 행은 1개로 간주</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>아래 '타게팅' 시트의 예시 행 참고(실제 답 아님, 채점 시 무시)</t>
         </is>
@@ -713,4 +738,164 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>가구원수</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>기준중위소득(월,원)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>중위소득150%_월상한(원)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>중위소득200%_월상한(원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2392013</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3588020</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4784026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3932658</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5898987</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7865316</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5025353</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7538030</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10050706</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6097773</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9146660</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12195546</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7108192</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10662288</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14216384</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8064805</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12097208</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16129610</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8988428</v>
+      </c>
+      <c r="C8" t="n">
+        <v>13482642</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17976856</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8인 이상</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1인 늘 때마다 (7인-6인)만큼 가산</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>가구원수로 직접 계산: 기준중위소득×%÷100, 원단위 반올림</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>